--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,136 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136874723</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kollheden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>404062</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6700942</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sofia Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sofia Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136874723</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -819,11 +819,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kollheden, Vrm</t>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2025 artfynd.xlsx
+++ b/artfynd/A 32328-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136874723</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
